--- a/output/pdf_financials_xlsx/PHX.xlsx
+++ b/output/pdf_financials_xlsx/PHX.xlsx
@@ -2391,10 +2391,10 @@
         <v>16.433</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>14.163</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>29.107</v>
       </c>
     </row>
     <row r="35">
@@ -2507,10 +2507,10 @@
         <v>16.433</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>14.163</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>29.107</v>
       </c>
     </row>
     <row r="37">
@@ -3203,10 +3203,10 @@
         <v>6.1</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>17.293</v>
+        <v>3.13</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>41.367</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="49">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/output/pdf_financials_xlsx/PHX.xlsx
+++ b/output/pdf_financials_xlsx/PHX.xlsx
@@ -1293,10 +1293,8 @@
       <c r="L16" s="3" t="n">
         <v>1.551122</v>
       </c>
-      <c r="M16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M16" s="3" t="n">
+        <v>-16.94928</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>49.600996</v>
@@ -1578,7 +1576,7 @@
         <v>36.566677</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>21.994897</v>
+        <v>21994.897</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-42488.845</v>
@@ -1595,10 +1593,8 @@
       <c r="L20" s="3" t="n">
         <v>-2.21312</v>
       </c>
-      <c r="M20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M20" s="3" t="n">
+        <v>-7.771157</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>23.317674</v>
@@ -1754,7 +1750,7 @@
         <v>36.566677</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>21.994897</v>
+        <v>21994.897</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-42488.845</v>
@@ -1771,10 +1767,8 @@
       <c r="L23" s="3" t="n">
         <v>-2.21312</v>
       </c>
-      <c r="M23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M23" s="3" t="n">
+        <v>-7.771157</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>22.724635</v>
@@ -1934,7 +1928,7 @@
         <v>29.729006</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>34.912535</v>
+        <v>34912.534921</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>38626.222727</v>
@@ -1951,10 +1945,8 @@
       <c r="L26" s="3" t="n">
         <v>55.328</v>
       </c>
-      <c r="M26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M26" s="3" t="n">
+        <v>51.807713</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>51.646898</v>
@@ -2013,10 +2005,8 @@
       <c r="L27" s="3" t="n">
         <v>1.551122</v>
       </c>
-      <c r="M27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M27" s="3" t="n">
+        <v>-16.94928</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>49.600996</v>
@@ -2131,10 +2121,8 @@
       <c r="L29" s="3" t="n">
         <v>41.39737</v>
       </c>
-      <c r="M29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M29" s="3" t="n">
+        <v>12.504598</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>75.46139599999999</v>
@@ -2191,10 +2179,8 @@
       <c r="L30" s="3" t="n">
         <v>11.43394474547597</v>
       </c>
-      <c r="M30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M30" s="3" t="n">
+        <v>5.074877033257726</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>22.1980494335297</v>
@@ -2251,10 +2237,8 @@
       <c r="L31" s="3" t="n">
         <v>242.6786545481271</v>
       </c>
-      <c r="M31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M31" s="3" t="n">
+        <v>-54.15051848810097</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>54.18512362130793</v>
@@ -2294,7 +2278,7 @@
         <v>9.606042087030495</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.004217891613327874</v>
+        <v>4.217891613327875</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>-14.81582489298571</v>
@@ -2311,10 +2295,8 @@
       <c r="L32" s="3" t="n">
         <v>-0.6112632709543574</v>
       </c>
-      <c r="M32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M32" s="3" t="n">
+        <v>-3.153853181137051</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>6.684776558982811</v>
@@ -6177,10 +6159,8 @@
       <c r="L99" s="3" t="n">
         <v>-2.21312</v>
       </c>
-      <c r="M99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M99" s="3" t="n">
+        <v>-7.771157</v>
       </c>
       <c r="N99" s="3" t="n">
         <v>22.724635</v>
@@ -6684,7 +6664,7 @@
         <v>0</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H108" s="3" t="n">
         <v>0</v>
@@ -7145,43 +7125,43 @@
         <v>0</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-4.344168</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-9.703989</v>
       </c>
       <c r="H116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-3.757344</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-2.916211</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-3.052146</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.06618</v>
       </c>
       <c r="M116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-1.852731</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-1.261</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0</v>
+        <v>-2.228</v>
       </c>
       <c r="R116" s="3" t="n">
-        <v>0</v>
+        <v>-4.699</v>
       </c>
     </row>
     <row r="117">
@@ -30966,7 +30946,11 @@
           <t>Acquisition of intangible assets (Note 6)</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -35000,7 +34984,11 @@
           <t>Acquisition of intangible assets (Note 7)</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -37455,7 +37443,11 @@
           <t>Acquisition of intangible assets (Note 8)</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -43596,7 +43588,11 @@
           <t>Cash generated from operating activities 64,660,664</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E361" t="inlineStr">
         <is>
           <t>-</t>
@@ -45828,7 +45824,11 @@
           <t>Impairment loss on goodwill (Note 7)</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr">
         <is>
           <t>-</t>
@@ -46333,7 +46333,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
@@ -47935,7 +47939,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -48432,7 +48440,11 @@
           <t>Acquisition of intangible assets 9</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E409" t="inlineStr">
         <is>
           <t>-</t>
@@ -50636,7 +50648,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E431" s="5" t="n">
         <v>-1.303976</v>
       </c>
@@ -58630,7 +58646,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E513" t="inlineStr">
         <is>
           <t>-</t>
@@ -62499,7 +62519,11 @@
           <t>Total income tax recovery $</t>
         </is>
       </c>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr">
         <is>
           <t>-</t>
@@ -62701,7 +62725,11 @@
           <t>Total income tax recovery</t>
         </is>
       </c>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E554" t="inlineStr">
         <is>
           <t>-</t>
@@ -65212,7 +65240,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D579" t="inlineStr"/>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E579" t="inlineStr">
         <is>
           <t>-</t>
